--- a/Parenting/postplanner-imports/cosp-postplanner-2026-07-20.xlsx
+++ b/Parenting/postplanner-imports/cosp-postplanner-2026-07-20.xlsx
@@ -478,7 +478,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/20/2026  13:15</t>
+          <t>07/20/2026  08:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -492,7 +492,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/20/2026  14:20</t>
+          <t>07/20/2026  08:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -506,7 +506,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/20/2026  15:25</t>
+          <t>07/20/2026  10:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -520,7 +520,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/20/2026  16:30</t>
+          <t>07/20/2026  10:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/20/2026  17:35</t>
+          <t>07/20/2026  12:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/20/2026  18:40</t>
+          <t>07/20/2026  14:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/20/2026  19:45</t>
+          <t>07/20/2026  16:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/20/2026  20:50</t>
+          <t>07/20/2026  16:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
